--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_297_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_297_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6115</v>
+        <v>6.5621</v>
       </c>
       <c r="E2" t="n">
-        <v>6.248</v>
+        <v>6.6018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3636</v>
+        <v>-0.0397</v>
       </c>
       <c r="G2" t="n">
         <v>3.8559</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0571</v>
+        <v>0.0077</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4973</v>
+        <v>0.094</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7634</v>
+        <v>3.2345</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8749</v>
+        <v>4.1109</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1116</v>
+        <v>-0.8763</v>
       </c>
       <c r="G3" t="n">
         <v>1.9262</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2324</v>
+        <v>0.2388</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0584</v>
+        <v>0.2937</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.605</v>
+        <v>1.2979</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2764</v>
+        <v>3.2311</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6714</v>
+        <v>-1.9332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8242</v>
+        <v>2.7119</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4598</v>
+        <v>0.6072</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6356000000000001</v>
+        <v>2.1047</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4502</v>
+        <v>4.5594</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7141</v>
+        <v>1.1868</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7361</v>
+        <v>3.3726</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.626</v>
+        <v>-1.8476</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2543</v>
+        <v>-0.5796</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3717</v>
+        <v>-1.2679</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8556</v>
+        <v>-0.803</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8442</v>
+        <v>-0.3104</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0114</v>
+        <v>-0.4927</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0026</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6341</v>
+        <v>0.2625</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8026</v>
+        <v>-0.3392</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1684</v>
+        <v>0.6017</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7119</v>
+        <v>0.3851</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6072</v>
+        <v>-0.2641</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1047</v>
+        <v>0.6492</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5594</v>
+        <v>0.346</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1868</v>
+        <v>0.2724</v>
       </c>
       <c r="L6" t="n">
-        <v>3.3726</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8476</v>
+        <v>0.0391</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5796</v>
+        <v>-0.5365</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2679</v>
+        <v>0.5756</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4668</v>
+        <v>-0.1199</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7389</v>
+        <v>-0.2908</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7279</v>
+        <v>0.1709</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0026</v>
+        <v>-0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0459</v>
+        <v>-0.0718</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4885</v>
+        <v>1.9357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5345</v>
+        <v>-2.0075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3851</v>
+        <v>0.8242</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2641</v>
+        <v>1.4598</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6492</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.346</v>
+        <v>2.4502</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2724</v>
+        <v>1.7141</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0736</v>
+        <v>0.7361</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0391</v>
+        <v>-1.626</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5365</v>
+        <v>-0.2543</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5756</v>
+        <v>-1.3717</v>
       </c>
       <c r="P7" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3365</v>
+        <v>0.1788</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>0.5034</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1037</v>
+        <v>-0.3246</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>-2.0026</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.416</v>
+        <v>-1.2928</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1704</v>
+        <v>-1.9464</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7543</v>
+        <v>0.6535</v>
       </c>
       <c r="G8" t="n">
         <v>0.6131</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8694</v>
+        <v>-0.7461</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8804</v>
+        <v>-0.6563</v>
       </c>
       <c r="U8" t="n">
-        <v>0.011</v>
+        <v>-0.0898</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4625</v>
+        <v>-2.1862</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1239</v>
+        <v>-2.0493</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3386</v>
+        <v>-0.1369</v>
       </c>
       <c r="G9" t="n">
         <v>0.4723</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.239</v>
+        <v>0.0373</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2161</v>
+        <v>-0.1415</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0228</v>
+        <v>0.1788</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4416</v>
+        <v>-3.2176</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8929</v>
+        <v>-2.6689</v>
       </c>
       <c r="F10" t="n">
         <v>-0.5487</v>
@@ -1234,10 +1234,10 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4639</v>
+        <v>-0.2399</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.2987</v>
       </c>
       <c r="U10" t="n">
         <v>0.0589</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4653</v>
+        <v>-4.1233</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5114</v>
+        <v>-4.1694</v>
       </c>
       <c r="F11" t="n">
         <v>0.0461</v>
@@ -1312,10 +1312,10 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3249</v>
+        <v>-0.9829</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8136</v>
+        <v>-0.4716</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5113</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6002</v>
+        <v>-6.0708</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1616</v>
+        <v>-6.7331</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5614</v>
+        <v>0.6623</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0747</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8685</v>
+        <v>-0.3391</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7389</v>
+        <v>-0.3104</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1296</v>
+        <v>-0.0288</v>
       </c>
       <c r="V12" t="n">
         <v>0.6778999999999999</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.927099999999998</v>
+        <v>-4.8069</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3955</v>
+        <v>-1.275500000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5315</v>
+        <v>-3.5314</v>
       </c>
       <c r="G13" t="n">
         <v>8.3843</v>
       </c>
       <c r="H13" t="n">
-        <v>5.774</v>
+        <v>5.774000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>2.6105</v>
@@ -1456,7 +1456,7 @@
         <v>-4.8482</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.569700000000001</v>
+        <v>-5.569699999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-5.798900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.9713</v>
+        <v>-2.8509</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5364</v>
+        <v>-2.4162</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4348000000000001</v>
+        <v>-0.4348</v>
       </c>
       <c r="V13" t="n">
         <v>-4.541300000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2217</v>
+        <v>7.497</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2146</v>
+        <v>4.3325</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0072</v>
+        <v>3.1645</v>
       </c>
       <c r="G14" t="n">
         <v>0.6853</v>
@@ -1546,13 +1546,13 @@
         <v>4.4071</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5544</v>
+        <v>0.8296</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4753</v>
+        <v>-0.3574</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0297</v>
+        <v>1.187</v>
       </c>
       <c r="V14" t="n">
         <v>3.8945</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0698</v>
+        <v>2.6085</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0223</v>
+        <v>2.672</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0475</v>
+        <v>-0.0635</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2695</v>
+        <v>-0.0122</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0492</v>
+        <v>0.4128</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7796999999999999</v>
+        <v>-0.4251</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7217</v>
+        <v>2.7042</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3599</v>
+        <v>1.6539</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3618</v>
+        <v>1.0504</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9912</v>
+        <v>-2.7165</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4091</v>
+        <v>-1.241</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5821</v>
+        <v>-1.4755</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4632</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6201</v>
+        <v>0.0553</v>
       </c>
       <c r="U15" t="n">
-        <v>0.843</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8197</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8197</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4741</v>
+        <v>1.8993</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7284</v>
+        <v>0.7653</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2544</v>
+        <v>1.134</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0122</v>
+        <v>-0.0252</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4128</v>
+        <v>1.437</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4251</v>
+        <v>-1.4621</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7042</v>
+        <v>1.115</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6539</v>
+        <v>1.6805</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0504</v>
+        <v>-0.5655</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7165</v>
+        <v>-1.1401</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.241</v>
+        <v>-0.2435</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4755</v>
+        <v>-0.8966</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4415</v>
+        <v>0.2133</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>-0.3497</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4468</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2556</v>
+        <v>1.104</v>
       </c>
       <c r="E17" t="n">
-        <v>1.039</v>
+        <v>0.921</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2166</v>
+        <v>0.183</v>
       </c>
       <c r="G17" t="n">
         <v>1.1103</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9133</v>
+        <v>0.7617</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6449</v>
+        <v>0.5269</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0794</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2935</v>
+        <v>-0.0393</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7859</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0252</v>
+        <v>-0.2695</v>
       </c>
       <c r="H18" t="n">
-        <v>1.437</v>
+        <v>-1.0492</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4621</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>1.115</v>
+        <v>1.7217</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6805</v>
+        <v>0.3599</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5655</v>
+        <v>1.3618</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1401</v>
+        <v>-1.9912</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2435</v>
+        <v>-1.4091</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8966</v>
+        <v>-0.5821</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6067</v>
+        <v>1.2336</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>0.5586</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2148</v>
+        <v>0.675</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>-0.8197</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.4128</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1058</v>
+        <v>-0.7199</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7173</v>
+        <v>1.1326</v>
       </c>
       <c r="G19" t="n">
         <v>-3.3864</v>
@@ -1936,13 +1936,13 @@
         <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5652</v>
+        <v>1.1549</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3135</v>
+        <v>0.4878</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2517</v>
+        <v>0.6671</v>
       </c>
       <c r="V19" t="n">
         <v>0.7886</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0474</v>
+        <v>0.2557</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1886</v>
+        <v>1.4245</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2361</v>
+        <v>-1.1689</v>
       </c>
       <c r="G20" t="n">
         <v>0.446</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1713</v>
+        <v>0.1318</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.086</v>
+        <v>-0.6985</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2893</v>
+        <v>0.0646</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7967</v>
+        <v>-0.7631</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0208</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2095</v>
+        <v>0.1779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0747</v>
+        <v>0.2792</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6975</v>
+        <v>-1.4736</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5008</v>
+        <v>-2.021</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1967</v>
+        <v>0.5473</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3125</v>
+        <v>-0.4928</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4059</v>
+        <v>-1.0983</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9067</v>
+        <v>0.6056</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4567</v>
+        <v>2.0449</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3095</v>
+        <v>0.1211</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1472</v>
+        <v>1.9238</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7692</v>
+        <v>-2.5377</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7153</v>
+        <v>-1.2195</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0539</v>
+        <v>-1.3182</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>0.847</v>
+        <v>-0.1975</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8259</v>
+        <v>-0.4991</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0211</v>
+        <v>0.3016</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3608</v>
+        <v>-2.0235</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4928</v>
+        <v>-1.2086</v>
       </c>
       <c r="F23" t="n">
-        <v>0.132</v>
+        <v>-0.8149</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4928</v>
+        <v>-1.3125</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0983</v>
+        <v>-0.4059</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6056</v>
+        <v>-0.9067</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0449</v>
+        <v>0.4567</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1211</v>
+        <v>0.3095</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9238</v>
+        <v>0.1472</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5377</v>
+        <v>-1.7692</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2195</v>
+        <v>-0.7153</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3182</v>
+        <v>-1.0539</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0846</v>
+        <v>0.521</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9709</v>
+        <v>0.1182</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1138</v>
+        <v>0.4028</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8048</v>
+        <v>-2.9221</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7778</v>
+        <v>-2.6598</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.027</v>
+        <v>-0.2623</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1064</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1419</v>
+        <v>0.0246</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6647</v>
+        <v>0.4294</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.927200000000001</v>
+        <v>7.499799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>3.531500000000001</v>
+        <v>3.5313</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3956</v>
+        <v>3.968200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-8.3842</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.773999999999999</v>
+        <v>-5.774</v>
       </c>
       <c r="I25" t="n">
         <v>-2.6102</v>
@@ -2380,7 +2380,7 @@
         <v>10.4178</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8482</v>
+        <v>4.848200000000001</v>
       </c>
       <c r="L25" t="n">
         <v>5.5697</v>
@@ -2404,16 +2404,16 @@
         <v>23.1954</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9714</v>
+        <v>5.543900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4348000000000001</v>
+        <v>0.4347999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5363</v>
+        <v>5.109</v>
       </c>
       <c r="V25" t="n">
-        <v>4.5413</v>
+        <v>4.541300000000001</v>
       </c>
       <c r="W25" t="n">
         <v>10.0752</v>
